--- a/06_Office_Related/01_NSO_work/06_SL_to_PIVOT_to_Compare_with_WP/02_GJ_WP_2026-27/SL 2.0/AMRELI.xlsx
+++ b/06_Office_Related/01_NSO_work/06_SL_to_PIVOT_to_Compare_with_WP/02_GJ_WP_2026-27/SL 2.0/AMRELI.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24729"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF3A429F-A139-4E7F-A8C9-D88217BF24EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C244F6B8-5D6A-4CD5-B074-3BB35DE29C7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3600" yWindow="2758" windowWidth="19562" windowHeight="10161" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CENTRAL 2.0" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="87">
   <si>
     <t>EXP</t>
   </si>
@@ -168,9 +168,6 @@
   </si>
   <si>
     <t>Babarpur</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>Khajuri</t>
@@ -629,6 +626,57 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -647,9 +695,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -677,12 +722,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -691,48 +730,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1016,44 +1013,44 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="14.33203125" customWidth="1"/>
+    <col min="3" max="3" width="14.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="44" t="s">
+    <row r="1" spans="1:12" ht="28.55" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="46"/>
-    </row>
-    <row r="2" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="47" t="s">
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="25"/>
+    </row>
+    <row r="2" spans="1:12" ht="28.55" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="48"/>
-      <c r="L2" s="49"/>
-    </row>
-    <row r="3" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="27"/>
+      <c r="L2" s="28"/>
+    </row>
+    <row r="3" spans="1:12" ht="28.55" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="29" t="s">
         <v>29</v>
       </c>
@@ -1069,13 +1066,13 @@
       <c r="K3" s="29"/>
       <c r="L3" s="29"/>
     </row>
-    <row r="4" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="50" t="s">
+    <row r="4" spans="1:12" ht="28.55" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="51"/>
+      <c r="B4" s="31"/>
       <c r="C4" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D4" s="29">
         <v>20</v>
@@ -1097,32 +1094,32 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="52"/>
-      <c r="B5" s="53"/>
+    <row r="5" spans="1:12" ht="28.55" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="32"/>
+      <c r="B5" s="33"/>
       <c r="C5" s="14"/>
-      <c r="D5" s="54" t="s">
+      <c r="D5" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="54"/>
-      <c r="F5" s="54" t="s">
+      <c r="E5" s="34"/>
+      <c r="F5" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54" t="s">
+      <c r="G5" s="34"/>
+      <c r="H5" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54" t="s">
-        <v>81</v>
-      </c>
-      <c r="K5" s="54"/>
+      <c r="I5" s="34"/>
+      <c r="J5" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="K5" s="34"/>
       <c r="L5" s="3">
         <f t="shared" ref="L5" si="0">B4+D4+F4+H4+J4</f>
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="32.6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>1</v>
       </c>
@@ -1158,7 +1155,7 @@
       </c>
       <c r="L6" s="1"/>
     </row>
-    <row r="7" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="19.05" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>5</v>
       </c>
@@ -1180,7 +1177,7 @@
         <v>2</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J7" s="7"/>
       <c r="K7" s="9"/>
@@ -1189,7 +1186,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" ht="19.05" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>5</v>
       </c>
@@ -1211,7 +1208,7 @@
         <v>2</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J8" s="7"/>
       <c r="K8" s="9"/>
@@ -1220,7 +1217,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" ht="19.05" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>8</v>
       </c>
@@ -1242,20 +1239,20 @@
         <v>2</v>
       </c>
       <c r="I9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="J9" s="7">
+        <v>2</v>
+      </c>
+      <c r="K9" s="8" t="s">
         <v>61</v>
-      </c>
-      <c r="J9" s="7">
-        <v>2</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>62</v>
       </c>
       <c r="L9" s="9">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" ht="19.05" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>8</v>
       </c>
@@ -1279,14 +1276,14 @@
         <v>2</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L10" s="9">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="19.05" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>11</v>
       </c>
@@ -1308,20 +1305,20 @@
         <v>2</v>
       </c>
       <c r="I11" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="J11" s="7">
+        <v>2</v>
+      </c>
+      <c r="K11" s="8" t="s">
         <v>62</v>
-      </c>
-      <c r="J11" s="7">
-        <v>2</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>63</v>
       </c>
       <c r="L11" s="9">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="19.05" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>11</v>
       </c>
@@ -1339,20 +1336,20 @@
         <v>2</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J12" s="7">
         <v>2</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L12" s="9">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="19.05" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>15</v>
       </c>
@@ -1370,26 +1367,24 @@
         <v>2</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J13" s="7"/>
-      <c r="K13" s="8" t="s">
-        <v>44</v>
-      </c>
+      <c r="K13" s="8"/>
       <c r="L13" s="9">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="19.05" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>16</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D14" s="7"/>
       <c r="E14" s="8"/>
@@ -1399,28 +1394,28 @@
         <v>2</v>
       </c>
       <c r="I14" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="J14" s="7">
+        <v>2</v>
+      </c>
+      <c r="K14" s="8" t="s">
         <v>65</v>
-      </c>
-      <c r="J14" s="7">
-        <v>2</v>
-      </c>
-      <c r="K14" s="8" t="s">
-        <v>66</v>
       </c>
       <c r="L14" s="9">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" ht="19.05" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>16</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D15" s="7">
         <v>2</v>
@@ -1436,22 +1431,22 @@
         <v>2</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L15" s="9">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" ht="19.05" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="6" t="s">
         <v>47</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>48</v>
       </c>
       <c r="D16" s="7">
         <v>2</v>
@@ -1465,28 +1460,28 @@
         <v>2</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J16" s="7">
         <v>2</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L16" s="9">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" ht="19.05" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D17" s="7">
         <v>2</v>
@@ -1499,23 +1494,21 @@
       <c r="H17" s="7"/>
       <c r="I17" s="3"/>
       <c r="J17" s="7"/>
-      <c r="K17" s="8" t="s">
-        <v>44</v>
-      </c>
+      <c r="K17" s="8"/>
       <c r="L17" s="9">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" ht="19.05" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>20</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D18" s="7"/>
       <c r="E18" s="8"/>
@@ -1525,20 +1518,20 @@
         <v>2</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J18" s="7">
         <v>2</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L18" s="9">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" ht="19.05" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>20</v>
       </c>
@@ -1546,7 +1539,7 @@
         <v>20</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D19" s="7">
         <v>2</v>
@@ -1562,22 +1555,22 @@
         <v>2</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L19" s="9">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" ht="19.05" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D20" s="7">
         <v>2</v>
@@ -1590,23 +1583,21 @@
       <c r="H20" s="7"/>
       <c r="I20" s="3"/>
       <c r="J20" s="7"/>
-      <c r="K20" s="8" t="s">
-        <v>44</v>
-      </c>
+      <c r="K20" s="8"/>
       <c r="L20" s="9">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" ht="19.05" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
@@ -1618,14 +1609,14 @@
         <v>2</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L21" s="9">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>22</v>
       </c>
@@ -1633,7 +1624,7 @@
         <v>22</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
@@ -1643,7 +1634,7 @@
         <v>2</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J22" s="7"/>
       <c r="K22" s="9"/>
@@ -1652,7 +1643,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2" t="s">
@@ -1683,23 +1674,23 @@
         <v>60</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="21" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:12" ht="21.1" x14ac:dyDescent="0.35">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
-      <c r="C24" s="55" t="s">
-        <v>84</v>
-      </c>
-      <c r="D24" s="56"/>
-      <c r="E24" s="56"/>
-      <c r="F24" s="56"/>
-      <c r="G24" s="56"/>
-      <c r="H24" s="56"/>
-      <c r="I24" s="57"/>
+      <c r="C24" s="37" t="s">
+        <v>83</v>
+      </c>
+      <c r="D24" s="38"/>
+      <c r="E24" s="38"/>
+      <c r="F24" s="38"/>
+      <c r="G24" s="38"/>
+      <c r="H24" s="38"/>
+      <c r="I24" s="39"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -1713,7 +1704,7 @@
       <c r="K25" s="5"/>
       <c r="L25" s="5"/>
     </row>
-    <row r="26" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" ht="19.05" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
         <v>24</v>
       </c>
@@ -1721,7 +1712,7 @@
         <v>24</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
@@ -1740,7 +1731,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" ht="19.05" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
         <v>24</v>
       </c>
@@ -1748,7 +1739,7 @@
         <v>24</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D27" s="7"/>
       <c r="E27" s="7"/>
@@ -1767,12 +1758,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A28" s="40" t="s">
-        <v>83</v>
-      </c>
-      <c r="B28" s="40"/>
-      <c r="C28" s="40"/>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" s="35" t="s">
+        <v>82</v>
+      </c>
+      <c r="B28" s="35"/>
+      <c r="C28" s="35"/>
       <c r="D28" s="15">
         <f>SUM(D26:D27)</f>
         <v>0</v>
@@ -1798,7 +1789,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -1812,12 +1803,12 @@
       <c r="K29" s="15"/>
       <c r="L29" s="15"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" s="40" t="s">
-        <v>82</v>
-      </c>
-      <c r="B30" s="40"/>
-      <c r="C30" s="40"/>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" s="35" t="s">
+        <v>81</v>
+      </c>
+      <c r="B30" s="35"/>
+      <c r="C30" s="35"/>
       <c r="D30" s="15">
         <f>+D23+D28</f>
         <v>20</v>
@@ -1843,21 +1834,21 @@
         <v>64</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="39" t="s">
-        <v>87</v>
-      </c>
-      <c r="B31" s="39"/>
-      <c r="C31" s="39"/>
-      <c r="D31" s="39"/>
-      <c r="E31" s="39"/>
-      <c r="F31" s="39"/>
-      <c r="G31" s="39"/>
-      <c r="H31" s="39"/>
-      <c r="I31" s="39"/>
-      <c r="J31" s="39"/>
-      <c r="K31" s="39"/>
-      <c r="L31" s="39"/>
+    <row r="31" spans="1:12" ht="33.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="36" t="s">
+        <v>86</v>
+      </c>
+      <c r="B31" s="36"/>
+      <c r="C31" s="36"/>
+      <c r="D31" s="36"/>
+      <c r="E31" s="36"/>
+      <c r="F31" s="36"/>
+      <c r="G31" s="36"/>
+      <c r="H31" s="36"/>
+      <c r="I31" s="36"/>
+      <c r="J31" s="36"/>
+      <c r="K31" s="36"/>
+      <c r="L31" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -1885,67 +1876,67 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="12.33203125" customWidth="1"/>
-    <col min="12" max="12" width="11.109375" customWidth="1"/>
+    <col min="3" max="3" width="12.375" customWidth="1"/>
+    <col min="12" max="12" width="11.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+    <row r="1" spans="1:12" ht="19.05" x14ac:dyDescent="0.25">
+      <c r="A1" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="28"/>
-    </row>
-    <row r="2" spans="1:12" ht="18" x14ac:dyDescent="0.3">
-      <c r="A2" s="23" t="s">
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="45"/>
+    </row>
+    <row r="2" spans="1:12" ht="19.05" x14ac:dyDescent="0.25">
+      <c r="A2" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="25"/>
-    </row>
-    <row r="3" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="33" t="s">
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
+      <c r="L2" s="42"/>
+    </row>
+    <row r="3" spans="1:12" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A3" s="49" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="33"/>
-      <c r="C3" s="33"/>
-      <c r="D3" s="33"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="33"/>
-      <c r="G3" s="33"/>
-      <c r="H3" s="33"/>
-      <c r="I3" s="33"/>
-      <c r="J3" s="33"/>
-      <c r="K3" s="33"/>
-      <c r="L3" s="33"/>
-    </row>
-    <row r="4" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="34" t="s">
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="49"/>
+      <c r="K3" s="49"/>
+      <c r="L3" s="49"/>
+    </row>
+    <row r="4" spans="1:12" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A4" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="35"/>
+      <c r="B4" s="51"/>
       <c r="C4" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D4" s="29">
         <v>10</v>
@@ -1967,32 +1958,32 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="36"/>
-      <c r="B5" s="37"/>
+    <row r="5" spans="1:12" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A5" s="52"/>
+      <c r="B5" s="53"/>
       <c r="C5" s="12"/>
-      <c r="D5" s="38" t="s">
+      <c r="D5" s="54" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="38"/>
-      <c r="F5" s="38" t="s">
+      <c r="E5" s="54"/>
+      <c r="F5" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="38"/>
-      <c r="H5" s="38" t="s">
+      <c r="G5" s="54"/>
+      <c r="H5" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="I5" s="38"/>
-      <c r="J5" s="38" t="s">
-        <v>81</v>
-      </c>
-      <c r="K5" s="38"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54" t="s">
+        <v>80</v>
+      </c>
+      <c r="K5" s="54"/>
       <c r="L5" s="3">
         <f t="shared" ref="L5" si="0">B4+D4+F4+H4+J4</f>
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>1</v>
       </c>
@@ -2030,7 +2021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
         <v>5</v>
       </c>
@@ -2048,7 +2039,7 @@
         <v>2</v>
       </c>
       <c r="I7" s="21" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J7" s="15"/>
       <c r="K7" s="15"/>
@@ -2057,12 +2048,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
         <v>5</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>7</v>
@@ -2084,7 +2075,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
         <v>8</v>
       </c>
@@ -2102,7 +2093,7 @@
         <v>2</v>
       </c>
       <c r="I9" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J9" s="15"/>
       <c r="K9" s="15"/>
@@ -2111,7 +2102,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
         <v>8</v>
       </c>
@@ -2129,20 +2120,20 @@
         <v>2</v>
       </c>
       <c r="I10" s="21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J10" s="15">
         <v>2</v>
       </c>
       <c r="K10" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L10" s="15">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
         <v>11</v>
       </c>
@@ -2166,19 +2157,19 @@
         <v>2</v>
       </c>
       <c r="K11" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L11" s="15">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C12" s="15" t="s">
         <v>14</v>
@@ -2191,20 +2182,20 @@
         <v>2</v>
       </c>
       <c r="I12" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J12" s="15">
         <v>2</v>
       </c>
       <c r="K12" s="21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L12" s="15">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
         <v>15</v>
       </c>
@@ -2228,19 +2219,19 @@
         <v>2</v>
       </c>
       <c r="K13" s="21" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L13" s="15">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
         <v>16</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C14" s="15" t="s">
         <v>17</v>
@@ -2259,14 +2250,14 @@
         <v>2</v>
       </c>
       <c r="K14" s="21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L14" s="15">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
         <v>18</v>
       </c>
@@ -2284,25 +2275,25 @@
         <v>2</v>
       </c>
       <c r="I15" s="21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J15" s="15">
         <v>2</v>
       </c>
       <c r="K15" s="21" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L15" s="15">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
         <v>20</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C16" s="15" t="s">
         <v>21</v>
@@ -2321,14 +2312,14 @@
         <v>2</v>
       </c>
       <c r="K16" s="21" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L16" s="15">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="15" t="s">
         <v>22</v>
       </c>
@@ -2346,7 +2337,7 @@
         <v>2</v>
       </c>
       <c r="I17" s="21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J17" s="15"/>
       <c r="K17" s="15"/>
@@ -2355,12 +2346,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="41" t="s">
-        <v>86</v>
-      </c>
-      <c r="B18" s="42"/>
-      <c r="C18" s="43"/>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="55" t="s">
+        <v>85</v>
+      </c>
+      <c r="B18" s="56"/>
+      <c r="C18" s="57"/>
       <c r="D18" s="20">
         <f>SUM(D7:D17)</f>
         <v>10</v>
@@ -2386,23 +2377,23 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="21" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" ht="21.1" x14ac:dyDescent="0.25">
       <c r="A19" s="15"/>
       <c r="B19" s="15"/>
-      <c r="C19" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="D19" s="31"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="31"/>
-      <c r="G19" s="31"/>
-      <c r="H19" s="31"/>
-      <c r="I19" s="32"/>
+      <c r="C19" s="46" t="s">
+        <v>84</v>
+      </c>
+      <c r="D19" s="47"/>
+      <c r="E19" s="47"/>
+      <c r="F19" s="47"/>
+      <c r="G19" s="47"/>
+      <c r="H19" s="47"/>
+      <c r="I19" s="48"/>
       <c r="J19" s="15"/>
       <c r="K19" s="15"/>
       <c r="L19" s="15"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
         <v>24</v>
       </c>
@@ -2428,7 +2419,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="15" t="s">
         <v>24</v>
       </c>
@@ -2454,12 +2445,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="40" t="s">
-        <v>83</v>
-      </c>
-      <c r="B22" s="40"/>
-      <c r="C22" s="40"/>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="35" t="s">
+        <v>82</v>
+      </c>
+      <c r="B22" s="35"/>
+      <c r="C22" s="35"/>
       <c r="D22" s="16">
         <f>SUM(D20:D21)</f>
         <v>0</v>
@@ -2485,7 +2476,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="15"/>
       <c r="B23" s="15"/>
       <c r="C23" s="15"/>
@@ -2499,12 +2490,12 @@
       <c r="K23" s="15"/>
       <c r="L23" s="15"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" s="40" t="s">
-        <v>82</v>
-      </c>
-      <c r="B24" s="40"/>
-      <c r="C24" s="40"/>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="35" t="s">
+        <v>81</v>
+      </c>
+      <c r="B24" s="35"/>
+      <c r="C24" s="35"/>
       <c r="D24" s="19">
         <f>+D18+D22</f>
         <v>10</v>
@@ -2530,21 +2521,21 @@
         <v>40</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" s="39" t="s">
-        <v>87</v>
-      </c>
-      <c r="B25" s="39"/>
-      <c r="C25" s="39"/>
-      <c r="D25" s="39"/>
-      <c r="E25" s="39"/>
-      <c r="F25" s="39"/>
-      <c r="G25" s="39"/>
-      <c r="H25" s="39"/>
-      <c r="I25" s="39"/>
-      <c r="J25" s="39"/>
-      <c r="K25" s="39"/>
-      <c r="L25" s="39"/>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" s="36" t="s">
+        <v>86</v>
+      </c>
+      <c r="B25" s="36"/>
+      <c r="C25" s="36"/>
+      <c r="D25" s="36"/>
+      <c r="E25" s="36"/>
+      <c r="F25" s="36"/>
+      <c r="G25" s="36"/>
+      <c r="H25" s="36"/>
+      <c r="I25" s="36"/>
+      <c r="J25" s="36"/>
+      <c r="K25" s="36"/>
+      <c r="L25" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="17">
